--- a/questionnaire_templates/007_study_app_setup_survey--questionnaire_templates.xlsx
+++ b/questionnaire_templates/007_study_app_setup_survey--questionnaire_templates.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -757,8 +757,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="23" customWidth="1" min="1" max="1"/>
-    <col width="50" customWidth="1" min="2" max="2"/>
-    <col width="50" customWidth="1" min="3" max="3"/>
+    <col width="10" customWidth="1" min="2" max="2"/>
+    <col width="10" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -786,12 +786,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'id':_1,_'name':_'plan_a',_'label':_'plan_a'}</t>
+          <t>plan_a</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'id': 1, 'name': 'plan_A', 'label': 'plan_A'}</t>
+          <t>plan A</t>
         </is>
       </c>
     </row>
@@ -803,12 +803,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'id':_2,_'name':_'plan_b',_'label':_'plan_b'}</t>
+          <t>plan_b</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'id': 2, 'name': 'plan_B', 'label': 'plan_B'}</t>
+          <t>plan B</t>
         </is>
       </c>
     </row>
@@ -820,12 +820,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'id':_3,_'name':_'plan_c',_'label':_'plan_c'}</t>
+          <t>plan_c</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'id': 3, 'name': 'plan_C', 'label': 'plan_C'}</t>
+          <t>plan C</t>
         </is>
       </c>
     </row>
@@ -837,12 +837,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'id':_1,_'name':_'pref_a',_'label':_'pref_a'}</t>
+          <t>pref_a</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'id': 1, 'name': 'pref_A', 'label': 'pref_A'}</t>
+          <t>pref A</t>
         </is>
       </c>
     </row>
@@ -854,12 +854,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'id':_2,_'name':_'pref_b',_'label':_'pref_b'}</t>
+          <t>pref_b</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'id': 2, 'name': 'pref_B', 'label': 'pref_B'}</t>
+          <t>pref B</t>
         </is>
       </c>
     </row>
@@ -871,12 +871,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'id':_3,_'name':_'pref_c',_'label':_'pref_c'}</t>
+          <t>pref_c</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'id': 3, 'name': 'pref_C', 'label': 'pref_C'}</t>
+          <t>pref C</t>
         </is>
       </c>
     </row>
@@ -888,12 +888,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'id':_4,_'name':_'pref_d',_'label':_'pref_d'}</t>
+          <t>pref_d</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'id': 4, 'name': 'pref_D', 'label': 'pref_D'}</t>
+          <t>pref D</t>
         </is>
       </c>
     </row>
@@ -905,12 +905,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'id':_1,_'name':_'access_a',_'label':_'access_a'}</t>
+          <t>access_a</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'id': 1, 'name': 'access_A', 'label': 'access_A'}</t>
+          <t>access A</t>
         </is>
       </c>
     </row>
@@ -922,12 +922,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'id':_2,_'name':_'access_b',_'label':_'access_b'}</t>
+          <t>access_b</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'id': 2, 'name': 'access_B', 'label': 'access_B'}</t>
+          <t>access B</t>
         </is>
       </c>
     </row>
@@ -939,12 +939,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>{'id':_3,_'name':_'access_c',_'label':_'access_c'}</t>
+          <t>access_c</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>{'id': 3, 'name': 'access_C', 'label': 'access_C'}</t>
+          <t>access C</t>
         </is>
       </c>
     </row>
@@ -956,12 +956,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>{'id':_4,_'name':_'access_d',_'label':_'access_d'}</t>
+          <t>access_d</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>{'id': 4, 'name': 'access_D', 'label': 'access_D'}</t>
+          <t>access D</t>
         </is>
       </c>
     </row>
